--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260208_201658.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
